--- a/paypal_payment_forms/047_paypal_coffee_order_form--paypal_payment_forms.xlsx
+++ b/paypal_payment_forms/047_paypal_coffee_order_form--paypal_payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -980,29 +980,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cappuccino</t>
+          <t>cold_brew</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cappuccino</t>
+          <t>Cold Brew</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>coffee_type_choices</t>
+          <t>size_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>cold_brew</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cold Brew</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1031,29 +1031,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>extra_large</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Extra Large</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>size_choices</t>
+          <t>milk_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>extra_large</t>
+          <t>half-and-half</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Extra Large</t>
+          <t>Half-and-half</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>half-and-half</t>
+          <t>whole</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Half-and-half</t>
+          <t>Whole</t>
         </is>
       </c>
     </row>
@@ -1082,29 +1082,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>whole</t>
+          <t>skim</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Whole</t>
+          <t>Skim</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>milk_choices</t>
+          <t>sugar_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>skim</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Skim</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>half</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Half</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>half</t>
+          <t>three-quarters</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Half</t>
+          <t>Three-quarters</t>
         </is>
       </c>
     </row>
@@ -1150,27 +1150,10 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>three-quarters</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
-        <is>
-          <t>Three-quarters</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>sugar_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
